--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.61940830794347</v>
+        <v>4.650653850040815</v>
       </c>
       <c r="D2" t="n">
-        <v>28.45648566026815</v>
+        <v>4.624178919793575</v>
       </c>
       <c r="E2" t="n">
-        <v>11.44594336735765</v>
+        <v>1.859965797195618</v>
       </c>
       <c r="F2" t="n">
-        <v>9.793742219243613</v>
+        <v>1.591483110627087</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.13702101023731</v>
+        <v>1.647265914163562</v>
       </c>
       <c r="D3" t="n">
-        <v>23.65258532651803</v>
+        <v>3.84354511555918</v>
       </c>
       <c r="E3" t="n">
-        <v>11.44594336735765</v>
+        <v>1.859965797195618</v>
       </c>
       <c r="F3" t="n">
-        <v>9.793742219243613</v>
+        <v>1.591483110627087</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.38730858725276</v>
+        <v>4.125437645428573</v>
       </c>
       <c r="D4" t="n">
-        <v>25.42333746670856</v>
+        <v>4.131292338340142</v>
       </c>
       <c r="E4" t="n">
-        <v>11.44594336735765</v>
+        <v>1.859965797195618</v>
       </c>
       <c r="F4" t="n">
-        <v>9.793742219243613</v>
+        <v>1.591483110627087</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>9.044431370544585</v>
+        <v>1.469720097713495</v>
       </c>
       <c r="D5" t="n">
-        <v>9.126751792453531</v>
+        <v>1.483097166273699</v>
       </c>
       <c r="E5" t="n">
-        <v>11.44594336735765</v>
+        <v>1.859965797195618</v>
       </c>
       <c r="F5" t="n">
-        <v>9.793742219243613</v>
+        <v>1.591483110627087</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.27645118243505</v>
+        <v>4.107423317145696</v>
       </c>
       <c r="D6" t="n">
-        <v>26.89928144845322</v>
+        <v>4.371133235373648</v>
       </c>
       <c r="E6" t="n">
-        <v>11.44594336735765</v>
+        <v>1.859965797195618</v>
       </c>
       <c r="F6" t="n">
-        <v>9.793742219243613</v>
+        <v>1.591483110627087</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.98492990491732</v>
+        <v>4.060051109549064</v>
       </c>
       <c r="D7" t="n">
-        <v>25.27844624122466</v>
+        <v>4.107747514199007</v>
       </c>
       <c r="E7" t="n">
-        <v>11.44594336735765</v>
+        <v>1.859965797195618</v>
       </c>
       <c r="F7" t="n">
-        <v>9.793742219243613</v>
+        <v>1.591483110627087</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.55368000772727</v>
+        <v>3.989973001255681</v>
       </c>
       <c r="D8" t="n">
-        <v>24.80554679293878</v>
+        <v>4.030901353852552</v>
       </c>
       <c r="E8" t="n">
-        <v>11.44594336735765</v>
+        <v>1.859965797195618</v>
       </c>
       <c r="F8" t="n">
-        <v>9.793742219243613</v>
+        <v>1.591483110627087</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.19742631404107</v>
+        <v>6.044581776031674</v>
       </c>
       <c r="D9" t="n">
-        <v>15.07112765817106</v>
+        <v>2.449058244452798</v>
       </c>
       <c r="E9" t="n">
-        <v>11.44594336735765</v>
+        <v>1.859965797195618</v>
       </c>
       <c r="F9" t="n">
-        <v>9.793742219243613</v>
+        <v>1.591483110627087</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>38.53883959114453</v>
+        <v>6.262561433560986</v>
       </c>
       <c r="D10" t="n">
-        <v>20.64258119678569</v>
+        <v>3.354419444477674</v>
       </c>
       <c r="E10" t="n">
-        <v>11.44594336735765</v>
+        <v>1.859965797195618</v>
       </c>
       <c r="F10" t="n">
-        <v>9.793742219243613</v>
+        <v>1.591483110627087</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>42.60935772168062</v>
+        <v>6.924020629773102</v>
       </c>
       <c r="D11" t="n">
-        <v>33.30628173510321</v>
+        <v>5.412270781954272</v>
       </c>
       <c r="E11" t="n">
-        <v>11.44594336735765</v>
+        <v>1.859965797195618</v>
       </c>
       <c r="F11" t="n">
-        <v>9.793742219243613</v>
+        <v>1.591483110627087</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>20.3005080850786</v>
+        <v>3.298832563825273</v>
       </c>
       <c r="D12" t="n">
-        <v>8.073707133470638</v>
+        <v>1.311977409188979</v>
       </c>
       <c r="E12" t="n">
-        <v>11.44594336735765</v>
+        <v>1.859965797195618</v>
       </c>
       <c r="F12" t="n">
-        <v>9.793742219243613</v>
+        <v>1.591483110627087</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.8641323297996</v>
+        <v>4.202921503592434</v>
       </c>
       <c r="D13" t="n">
-        <v>19.88857852023507</v>
+        <v>3.231894009538199</v>
       </c>
       <c r="E13" t="n">
-        <v>11.44594336735765</v>
+        <v>1.859965797195618</v>
       </c>
       <c r="F13" t="n">
-        <v>9.793742219243613</v>
+        <v>1.591483110627087</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>26.00394621225393</v>
+        <v>4.225641259491263</v>
       </c>
       <c r="D14" t="n">
-        <v>16.33617538699518</v>
+        <v>2.654628500386716</v>
       </c>
       <c r="E14" t="n">
-        <v>11.44594336735765</v>
+        <v>1.859965797195618</v>
       </c>
       <c r="F14" t="n">
-        <v>9.793742219243613</v>
+        <v>1.591483110627087</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>48.99464377708955</v>
+        <v>7.961629613777053</v>
       </c>
       <c r="D15" t="n">
-        <v>45.2822732711136</v>
+        <v>7.358369406555961</v>
       </c>
       <c r="E15" t="n">
-        <v>11.44594336735765</v>
+        <v>1.859965797195618</v>
       </c>
       <c r="F15" t="n">
-        <v>9.793742219243613</v>
+        <v>1.591483110627087</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>24.88366768982796</v>
+        <v>4.043595999597043</v>
       </c>
       <c r="D16" t="n">
-        <v>26.40432108743369</v>
+        <v>4.290702176707975</v>
       </c>
       <c r="E16" t="n">
-        <v>11.44594336735765</v>
+        <v>1.859965797195618</v>
       </c>
       <c r="F16" t="n">
-        <v>9.793742219243613</v>
+        <v>1.591483110627087</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>5.375644159628803</v>
+        <v>0.8735421759396805</v>
       </c>
       <c r="D17" t="n">
-        <v>4.659846027713304</v>
+        <v>0.7572249795034121</v>
       </c>
       <c r="E17" t="n">
-        <v>11.44594336735765</v>
+        <v>1.859965797195618</v>
       </c>
       <c r="F17" t="n">
-        <v>9.793742219243613</v>
+        <v>1.591483110627087</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
